--- a/DIA03S.xlsx
+++ b/DIA03S.xlsx
@@ -412,7 +412,7 @@
     <t>20077483</t>
   </si>
   <si>
-    <t>MERRIES PANT GS26 XL</t>
+    <t>MRRIES PANTG 26'S XL</t>
   </si>
   <si>
     <t>20112938</t>

--- a/DIA03S.xlsx
+++ b/DIA03S.xlsx
@@ -19,7 +19,7 @@
     <t>20024306</t>
   </si>
   <si>
-    <t>MAMY/P PANT BOY XL24</t>
+    <t>MMY/P PNT BY 24'S XL</t>
   </si>
   <si>
     <t>DIA03S</t>
@@ -37,13 +37,13 @@
     <t>20024303</t>
   </si>
   <si>
-    <t>MAMY/P PANT BOY L28</t>
+    <t>MMY/P PNT BOY 28'S L</t>
   </si>
   <si>
     <t>20121396</t>
   </si>
   <si>
-    <t>MAMY POKO SC M32+2'S</t>
+    <t>MAMY/P SC 32+2'S M</t>
   </si>
   <si>
     <t>3</t>
@@ -52,7 +52,7 @@
     <t>20121399</t>
   </si>
   <si>
-    <t>MAMY POKO SC L 28'S</t>
+    <t>MAMY/P SC 28'S L</t>
   </si>
   <si>
     <t>4</t>
@@ -85,19 +85,19 @@
     <t>20095875</t>
   </si>
   <si>
-    <t>MP PANTS T/G 28'S L</t>
+    <t>MMY/P PNT T/G 28'S L</t>
   </si>
   <si>
     <t>20095874</t>
   </si>
   <si>
-    <t>MP PANTS T/G 30'S M</t>
+    <t>MMY/P PNT T/G 30'S M</t>
   </si>
   <si>
     <t>20045421</t>
   </si>
   <si>
-    <t>MAMY/P PNT/STD XXL24</t>
+    <t>MMY/P PT SD 24'S XXL</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
@@ -106,7 +106,7 @@
     <t>20106150</t>
   </si>
   <si>
-    <t>MAMY POKO 44'S NB</t>
+    <t>MAMY/P 44'S NBORN</t>
   </si>
   <si>
     <t>20045423</t>
@@ -121,19 +121,19 @@
     <t>20045418</t>
   </si>
   <si>
-    <t>MAMY/P PANTS STD S38</t>
+    <t>MMY/P PNT STD 38'S S</t>
   </si>
   <si>
     <t>20045419</t>
   </si>
   <si>
-    <t>MAMY/P PANTS STD M32</t>
+    <t>MMY/P PNT STD 32'S M</t>
   </si>
   <si>
     <t>20045422</t>
   </si>
   <si>
-    <t>MAMY/P PANTS STD L28</t>
+    <t>MMY/P PNT STD 28'S L</t>
   </si>
   <si>
     <t>20064973</t>
@@ -169,7 +169,7 @@
     <t>20095876</t>
   </si>
   <si>
-    <t>MP PANTS T/G 23S XL</t>
+    <t>MMY/P PNT TG 23'S XL</t>
   </si>
   <si>
     <t>20041257</t>
@@ -256,13 +256,13 @@
     <t>20092521</t>
   </si>
   <si>
-    <t>SWEETY SLV PANT 28 L</t>
+    <t>SWEETY S PANT 28'S L</t>
   </si>
   <si>
     <t>20092520</t>
   </si>
   <si>
-    <t>SWEETY SLV PANT 32 M</t>
+    <t>SWEETY S PANT 32'S M</t>
   </si>
   <si>
     <t>20083489</t>
@@ -283,7 +283,7 @@
     <t>20083937</t>
   </si>
   <si>
-    <t>SWEETY SLV PANT 24XL</t>
+    <t>SWEETY S PNT 24'S XL</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
@@ -307,19 +307,19 @@
     <t>20137024</t>
   </si>
   <si>
-    <t>SWEETY X-PRT M-44</t>
+    <t>SWEETY X-PRT 44'S M</t>
   </si>
   <si>
     <t>20137023</t>
   </si>
   <si>
-    <t>SWEETY X-PERT L-38</t>
+    <t>SWEETY X-PERT 38'S L</t>
   </si>
   <si>
     <t>20140872</t>
   </si>
   <si>
-    <t>SWEETY X-PRT XL-32S</t>
+    <t>SWEETY X-PRT 32'S XL</t>
   </si>
   <si>
     <t>20108881</t>
